--- a/Testing_Practice_Project.xlsx
+++ b/Testing_Practice_Project.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -872,6 +872,208 @@
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Checkout with valid details</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as standard_user / secret_sauce
+2. Add one product to cart
+3. Open cart and click Checkout
+4. Enter First Name: Rahul, Last Name: Shah, Postal Code: 400001
+5. Click Continue</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Overview page opens</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Overview page opened</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Checkout with empty First Name</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1. On the checkout form leave First Name empty
+2. Enter Last Name and Postal Code
+3. Click Continue</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Error: First Name is required</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Error: First Name is required</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Checkout with empty Last Name</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave Last Name empty
+2. Enter First Name and Postal Code
+3. Click Continue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Error: Last Name is required</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Error: Last Name is required</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Checkout with empty Postal Code</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave Postal Code empty
+2. Enter First Name and Last Name
+3. Click Continue</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Error: Postal Code is required</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Error: Postal Code is required</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TC16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Order total is correct</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1. On the overview page check Item total, Tax and Total</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Item total + Tax = Total</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Item total $29.99 + Tax $2.40 = Total $32.39</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Complete the order</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1. On the overview page click Finish</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Message: Thank you for your order!</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Message: Thank you for your order!</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/Testing_Practice_Project.xlsx
+++ b/Testing_Practice_Project.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1077,6 +1077,205 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Login with locked out user</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1. Open saucedemo.com
+2. Login with locked_out_user / secret_sauce</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Error shown that the user is locked out, no login</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Error shown, user could not login</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Login time for performance_glitch_user</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1. Login with performance_glitch_user / secret_sauce</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Login completes within a few seconds</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Login took about 5 to 6 seconds</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TC20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Sort products by Price low to high (problem_user)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as problem_user / secret_sauce
+2. Select Price (low to high) from the sort dropdown</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Products are shown from lowest to highest price</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Products are not sorted by price</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TC21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Fill checkout form (problem_user)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as problem_user
+2. Add a product, open cart, click Checkout
+3. Enter First Name, Last Name and Postal Code</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>All three fields keep the typed values, user can continue</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Last Name could not be typed</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TC22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Complete an order (error_user)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as error_user / secret_sauce (new Incognito window)
+2. Add a product, click Checkout, enter details, click Continue
+3. Click Finish</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Order completes with message: Thank you for your order!</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Last Name could not be typed. Continue worked, but clicking Finish did nothing and the order was not completed. Only 3 items could be removed from the cart.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Page and cart check (visual_user)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as visual_user / secret_sauce
+2. Compare the products page and cart with standard_user</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Cart is empty and the page looks the same as for standard_user</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Cart already had 3 items from the previous user</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1088,7 +1287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1267,6 +1466,223 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BUG03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Products are not sorted correctly when Price (low to high) is selected for problem_user</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1. Open saucedemo.com
+2. Login with problem_user / secret_sauce
+3. Select Price (low to high) from the sort dropdown</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Products are shown in order from lowest to highest price.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The products are not sorted by price.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>BUG03_sorting.png</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>KAN-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BUG04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Last Name field does not work correctly on the checkout form for problem_user</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1. Open saucedemo.com
+2. Login with problem_user / secret_sauce
+3. Add a product and click Checkout
+4. Enter First Name, Last Name and Postal Code</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>All three fields keep the typed values and the user can continue.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The Last Name could not be typed. Also seen with error_user.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>BUG04_last_name.png</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>KAN-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BUG05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Cart items from one user are shown after logging in as another user</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as standard_user and add 3 products
+2. Logout
+3. Login as visual_user</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>The new user cart is empty.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The cart already shows the 3 products added by the previous user.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>BUG05_cart_carry_over.png</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>KAN-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BUG06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Finish button does not complete the order for error_user</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as error_user / secret_sauce
+2. Add a product, click Checkout, enter details, click Continue
+3. Click Finish</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Order is completed and Thank you for your order! is shown.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Nothing happens on clicking Finish. The order is not completed.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>BUG06_finish_not_working.png</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>KAN-9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
